--- a/data/dividends_info_20261004.xlsx
+++ b/data/dividends_info_20261004.xlsx
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,7 +1705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1715,14 +1715,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1773,58 +1773,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1858,46 +1858,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1909,46 +1909,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1960,29 +1960,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1994,148 +1994,148 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2164,46 +2164,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2215,29 +2215,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2283,46 +2283,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2334,29 +2334,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2368,63 +2368,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2436,12 +2436,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2453,114 +2453,114 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2572,46 +2572,46 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2623,63 +2623,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,12 +2691,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2708,143 +2708,143 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2871,19 +2871,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2895,29 +2895,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2929,29 +2929,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2963,80 +2963,80 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3058,19 +3058,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3082,12 +3082,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3116,12 +3116,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3133,29 +3133,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3184,29 +3184,29 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3218,12 +3218,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3235,68 +3235,238 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>OPS ECOM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BIESSE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Lottomatica Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Nusco S.p.A.</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>2026-11-03</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Lottomatica Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>JUVENTUS F.C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3324,146 +3494,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>